--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484813_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484813_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1797</v>
+        <v>2.4275</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0938</v>
+        <v>1.2887</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0859</v>
+        <v>1.1388</v>
       </c>
       <c r="G2" t="n">
         <v>1.1864</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0823</v>
+        <v>0.1655</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7055</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6231</v>
+        <v>0.6761</v>
       </c>
       <c r="V2" t="n">
         <v>0.3208</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8937</v>
+        <v>2.1822</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2125</v>
+        <v>1.3687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6812</v>
+        <v>0.8135</v>
       </c>
       <c r="G3" t="n">
         <v>2.053</v>
@@ -688,13 +688,13 @@
         <v>0.3774</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5367</v>
+        <v>-0.2482</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.164</v>
+        <v>-0.0078</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3727</v>
+        <v>-0.2404</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>0.9568</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0097</v>
+        <v>1.5813</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8098</v>
+        <v>-0.6246</v>
       </c>
       <c r="G4" t="n">
         <v>0.7003</v>
@@ -766,13 +766,13 @@
         <v>0.9435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2316</v>
+        <v>-0.0116</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.2364</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4332</v>
+        <v>-0.248</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6855</v>
+        <v>-1.0042</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5175</v>
+        <v>-0.8098</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1679</v>
+        <v>-0.1944</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5548</v>
@@ -844,13 +844,13 @@
         <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5485</v>
+        <v>0.2297</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0559</v>
+        <v>-0.3482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6044</v>
+        <v>0.5779</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2452</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>V. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5887</v>
+        <v>-2.1408</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9822</v>
+        <v>-2.6867</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6065</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.47</v>
+        <v>-1.7043</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.8361</v>
+        <v>0.0141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3662</v>
+        <v>-1.7184</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7629</v>
+        <v>-0.2409</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3884</v>
+        <v>0.2441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6254999999999999</v>
+        <v>-0.485</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7071</v>
+        <v>-1.4634</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4478</v>
+        <v>-0.23</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2593</v>
+        <v>-1.2334</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9341</v>
+        <v>-0.6287</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6677</v>
+        <v>-0.483</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2664</v>
+        <v>-0.1457</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6754</v>
+        <v>-0.7513</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.0193</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6754</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. GALVEZ ARROYO</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6384</v>
+        <v>-2.7121</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9992</v>
+        <v>-0.9194</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3607</v>
+        <v>-1.7927</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7043</v>
+        <v>-3.3627</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0141</v>
+        <v>-2.2868</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7184</v>
+        <v>-1.0759</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2409</v>
+        <v>-0.8389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2441</v>
+        <v>-1.4729</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.485</v>
+        <v>0.634</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4634</v>
+        <v>-2.5238</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.23</v>
+        <v>-0.8139</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2334</v>
+        <v>-1.7099</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1263</v>
+        <v>-0.4099</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7955</v>
+        <v>-0.3823</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3309</v>
+        <v>-0.0276</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7513</v>
+        <v>-0.0717</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.0193</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>0.268</v>
+        <v>-0.3736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2581</v>
+        <v>-3.3094</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4653</v>
+        <v>-2.7029</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7927</v>
+        <v>-0.6065</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3627</v>
+        <v>-2.47</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2868</v>
+        <v>-2.8361</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0759</v>
+        <v>0.3662</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8389</v>
+        <v>-0.7629</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4729</v>
+        <v>-1.3884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.634</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5238</v>
+        <v>-1.7071</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8139</v>
+        <v>-1.4478</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7099</v>
+        <v>-0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9558</v>
+        <v>0.2134</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9283</v>
+        <v>-0.053</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0276</v>
+        <v>0.2664</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0717</v>
+        <v>-0.6754</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3736</v>
+        <v>-0.6754</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7114</v>
+        <v>-4.2468</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8468</v>
+        <v>-4.8267</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1354</v>
+        <v>0.5798</v>
       </c>
       <c r="G9" t="n">
         <v>0.7415</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0383</v>
+        <v>-0.4971</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7367</v>
+        <v>-0.7165</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7749</v>
+        <v>0.2194</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3398</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.0654</v>
+        <v>-7.2394</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1976</v>
+        <v>-5.398</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8678</v>
+        <v>-1.8414</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1606</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5878</v>
+        <v>-0.7617</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.445</v>
+        <v>-0.6454</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1427</v>
+        <v>-0.1163</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2414</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.6741</v>
+        <v>-15.0862</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.6926</v>
+        <v>-13.1048</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9815</v>
+        <v>-1.9816</v>
       </c>
       <c r="G11" t="n">
         <v>-5.571200000000001</v>
@@ -1282,7 +1282,7 @@
         <v>-0.4853000000000003</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.086</v>
+        <v>-5.085999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>1.2605</v>
@@ -1291,7 +1291,7 @@
         <v>2.7779</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.517300000000001</v>
+        <v>-1.5173</v>
       </c>
       <c r="M11" t="n">
         <v>-6.831900000000001</v>
@@ -1300,10 +1300,10 @@
         <v>-3.2633</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.5687</v>
+        <v>-3.568699999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.887</v>
+        <v>-1.886999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.2655</v>
@@ -1312,16 +1312,16 @@
         <v>10.3785</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5364</v>
+        <v>-1.9486</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.4984</v>
+        <v>-2.9104</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9617</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.679399999999999</v>
+        <v>-5.6794</v>
       </c>
       <c r="W11" t="n">
         <v>0.8105</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.540900000000001</v>
+        <v>10.6968</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1588</v>
+        <v>6.8408</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3821</v>
+        <v>3.856</v>
       </c>
       <c r="G12" t="n">
         <v>4.1484</v>
@@ -1390,13 +1390,13 @@
         <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0793</v>
+        <v>0.0766</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1046</v>
+        <v>-0.4226</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0253</v>
+        <v>0.4992</v>
       </c>
       <c r="V12" t="n">
         <v>4.3962</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.0814</v>
+        <v>8.6172</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0299</v>
+        <v>6.2776</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0516</v>
+        <v>2.3396</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1028</v>
+        <v>4.0279</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0072</v>
+        <v>0.9587</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0956</v>
+        <v>3.0692</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9377</v>
+        <v>3.7814</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4485</v>
+        <v>1.1888</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4892</v>
+        <v>2.5927</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1651</v>
+        <v>0.2465</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4413</v>
+        <v>-0.23</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4765</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9221</v>
+        <v>0.5514</v>
       </c>
       <c r="T13" t="n">
-        <v>2.734</v>
+        <v>0.0058</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1882</v>
+        <v>0.5456</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2452</v>
+        <v>2.5284</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2452</v>
+        <v>2.4904</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2676</v>
+        <v>5.7841</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1084</v>
+        <v>3.0812</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1592</v>
+        <v>2.7029</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0279</v>
+        <v>3.1028</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9587</v>
+        <v>1.0072</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0692</v>
+        <v>2.0956</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7814</v>
+        <v>2.9377</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1888</v>
+        <v>1.4485</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5927</v>
+        <v>1.4892</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2465</v>
+        <v>0.1651</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.23</v>
+        <v>-0.4413</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4765</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5096</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7983</v>
+        <v>1.6248</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1634</v>
+        <v>0.7853</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3651</v>
+        <v>0.8395</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5284</v>
+        <v>1.2452</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4904</v>
+        <v>1.2452</v>
       </c>
       <c r="X14" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2463</v>
+        <v>0.9326</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1696</v>
+        <v>0.2029</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4159</v>
+        <v>0.7297</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4013</v>
+        <v>0.1109</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7153</v>
+        <v>-0.3827</v>
       </c>
       <c r="I15" t="n">
-        <v>0.314</v>
+        <v>0.4936</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.7723</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0.1057</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2057</v>
+        <v>0.6666</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2696</v>
+        <v>-0.6614</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1612</v>
+        <v>-0.4883</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1083</v>
+        <v>-0.173</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2327</v>
+        <v>-0.1408</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8411999999999999</v>
+        <v>-0.5694</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3916</v>
+        <v>0.4286</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6036</v>
+        <v>0.019</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6969</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3607</v>
+        <v>-0.5593</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0576</v>
+        <v>1.4136</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4111</v>
+        <v>-0.4013</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3013</v>
+        <v>-0.7153</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7124</v>
+        <v>0.314</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8784</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5125999999999999</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3658</v>
+        <v>0.2057</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4673</v>
+        <v>0.2696</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8139</v>
+        <v>0.1612</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3466</v>
+        <v>0.1083</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6983</v>
+        <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>0.418</v>
+        <v>0.8406</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4086</v>
+        <v>0.4514</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8266</v>
+        <v>0.3892</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4491</v>
+        <v>0.6239</v>
       </c>
       <c r="E17" t="n">
-        <v>0.008</v>
+        <v>-0.9058</v>
       </c>
       <c r="F17" t="n">
-        <v>0.441</v>
+        <v>1.5297</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1109</v>
+        <v>0.3996</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3827</v>
+        <v>1.296</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4936</v>
+        <v>-0.8963</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7723</v>
+        <v>0.6826</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1057</v>
+        <v>1.8172</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6666</v>
+        <v>-1.1346</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6614</v>
+        <v>-0.2829</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4883</v>
+        <v>-0.5212</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.173</v>
+        <v>0.2383</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6243</v>
+        <v>0.0356</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7642</v>
+        <v>-0.0033</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1399</v>
+        <v>0.0388</v>
       </c>
       <c r="V17" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0.019</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2493</v>
+        <v>0.2194</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4904</v>
+        <v>-1.653</v>
       </c>
       <c r="F18" t="n">
-        <v>1.241</v>
+        <v>1.8724</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3996</v>
+        <v>1.4111</v>
       </c>
       <c r="H18" t="n">
-        <v>1.296</v>
+        <v>-0.3013</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8963</v>
+        <v>1.7124</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6826</v>
+        <v>1.8784</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8172</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1346</v>
+        <v>1.3658</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2829</v>
+        <v>-0.4673</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5212</v>
+        <v>-0.8139</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2383</v>
+        <v>0.3466</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8377</v>
+        <v>-0.0595</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5879</v>
+        <v>-0.7009</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2498</v>
+        <v>0.6414</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9066</v>
+        <v>-1.3702</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5526</v>
+        <v>-2.3577</v>
       </c>
       <c r="F19" t="n">
-        <v>0.646</v>
+        <v>0.9875</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4476</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4591</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6314</v>
+        <v>-0.4366</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1723</v>
+        <v>0.5139</v>
       </c>
       <c r="V19" t="n">
         <v>-1.566</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3948</v>
+        <v>-4.0412</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4823</v>
+        <v>-4.2875</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0876</v>
+        <v>0.2463</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5648</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1881</v>
+        <v>0.1655</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1646</v>
+        <v>0.3233</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0574</v>
+        <v>-5.3437</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.268</v>
+        <v>-4.6577</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7894</v>
+        <v>-0.6859</v>
       </c>
       <c r="G21" t="n">
         <v>-5.2157</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9505</v>
+        <v>0.6643</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4761</v>
+        <v>0.0864</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4744</v>
+        <v>0.5779</v>
       </c>
       <c r="V21" t="n">
         <v>-1.547</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.6741</v>
+        <v>16.9732</v>
       </c>
       <c r="E22" t="n">
-        <v>1.981500000000001</v>
+        <v>1.9815</v>
       </c>
       <c r="F22" t="n">
-        <v>13.6926</v>
+        <v>14.9918</v>
       </c>
       <c r="G22" t="n">
         <v>5.571299999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4852000000000003</v>
+        <v>0.4851999999999994</v>
       </c>
       <c r="I22" t="n">
-        <v>5.0861</v>
+        <v>5.086099999999998</v>
       </c>
       <c r="J22" t="n">
         <v>6.8318</v>
@@ -2170,22 +2170,22 @@
         <v>12.2655</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5365</v>
+        <v>3.8358</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9615000000000002</v>
+        <v>-0.9618</v>
       </c>
       <c r="U22" t="n">
-        <v>3.4982</v>
+        <v>4.7974</v>
       </c>
       <c r="V22" t="n">
-        <v>5.6794</v>
+        <v>5.679400000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>6.489800000000001</v>
+        <v>6.489800000000002</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8104000000000001</v>
+        <v>-0.8104000000000002</v>
       </c>
     </row>
   </sheetData>
